--- a/excel files/Verifications & validations/Products/Nursery_Feeder_Test_Cases.xlsx
+++ b/excel files/Verifications & validations/Products/Nursery_Feeder_Test_Cases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nutreco1-my.sharepoint.com/personal/akashrai_sarvesh_eruvaka_com/Documents/Documents/2026_Project/Moving Feeder/MF_Test Cases/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2024" documentId="8_{EA694135-9146-429E-AB7B-725BF0A71DC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F74B23B-68B5-4536-858B-91A1E61AD6C5}"/>
+  <xr:revisionPtr revIDLastSave="2032" documentId="8_{EA694135-9146-429E-AB7B-725BF0A71DC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C66AC50-C934-4479-B87F-3A527209ED2B}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="7" activeTab="5" xr2:uid="{BD55DB27-4D39-4597-972E-029B203F14CF}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="8" xr2:uid="{BD55DB27-4D39-4597-972E-029B203F14CF}"/>
   </bookViews>
   <sheets>
     <sheet name="Testings Info" sheetId="14" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3626" uniqueCount="2427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3618" uniqueCount="2427">
   <si>
     <t>ADD cases</t>
   </si>
@@ -28947,9 +28947,7 @@
         <v>1566</v>
       </c>
       <c r="I9" s="7"/>
-      <c r="J9" s="7" t="s">
-        <v>73</v>
-      </c>
+      <c r="J9" s="7"/>
       <c r="K9" s="7"/>
       <c r="L9" s="81"/>
       <c r="M9" s="12"/>
@@ -28986,9 +28984,7 @@
         <v>1571</v>
       </c>
       <c r="I10" s="7"/>
-      <c r="J10" s="7" t="s">
-        <v>73</v>
-      </c>
+      <c r="J10" s="7"/>
       <c r="K10" s="7"/>
       <c r="L10" s="81"/>
       <c r="M10" s="12"/>
@@ -29025,9 +29021,7 @@
         <v>1576</v>
       </c>
       <c r="I11" s="7"/>
-      <c r="J11" s="7" t="s">
-        <v>73</v>
-      </c>
+      <c r="J11" s="7"/>
       <c r="K11" s="7"/>
       <c r="L11" s="81"/>
       <c r="M11" s="12"/>
@@ -29064,9 +29058,7 @@
         <v>1582</v>
       </c>
       <c r="I12" s="7"/>
-      <c r="J12" s="7" t="s">
-        <v>73</v>
-      </c>
+      <c r="J12" s="7"/>
       <c r="K12" s="7"/>
       <c r="L12" s="81"/>
       <c r="M12" s="12"/>
@@ -29181,9 +29173,7 @@
         <v>1597</v>
       </c>
       <c r="I15" s="7"/>
-      <c r="J15" s="7" t="s">
-        <v>73</v>
-      </c>
+      <c r="J15" s="7"/>
       <c r="K15" s="7"/>
       <c r="L15" s="81"/>
       <c r="M15" s="12"/>
@@ -29610,9 +29600,7 @@
         <v>1662</v>
       </c>
       <c r="I26" s="7"/>
-      <c r="J26" s="7" t="s">
-        <v>73</v>
-      </c>
+      <c r="J26" s="7"/>
       <c r="K26" s="7"/>
       <c r="L26" s="81"/>
       <c r="M26" s="12"/>
@@ -29649,9 +29637,7 @@
         <v>1669</v>
       </c>
       <c r="I27" s="7"/>
-      <c r="J27" s="7" t="s">
-        <v>73</v>
-      </c>
+      <c r="J27" s="7"/>
       <c r="K27" s="7"/>
       <c r="L27" s="81"/>
       <c r="M27" s="12"/>
@@ -29688,9 +29674,7 @@
         <v>1675</v>
       </c>
       <c r="I28" s="7"/>
-      <c r="J28" s="7" t="s">
-        <v>73</v>
-      </c>
+      <c r="J28" s="7"/>
       <c r="K28" s="7"/>
       <c r="L28" s="81"/>
       <c r="M28" s="12"/>
